--- a/flujo-incentivos-volanteo.xlsx
+++ b/flujo-incentivos-volanteo.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Resumen" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Escenario Actual" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Estrategias por Quincena" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Datos de Campo (Rodrigo)" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="89">
   <si>
     <t xml:space="preserve">Incentivos de Volanteo - Escenario Actual y Estrategias de Pago</t>
   </si>
@@ -190,20 +191,124 @@
   </si>
   <si>
     <t xml:space="preserve">Nota: con estos 4 ejemplos (2 meses), se ve que las 3 estrategias reparten el mismo dinero de forma distinta segun que tan rapido llega el equipo a cada umbral. Cambia los dias de ejemplo por tus datos reales para comparar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datos de Campo - Reunion con Rodrigo (24 set.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAMETROS REALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personas fijas confirmadas (Marcia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta individual (volanteos/persona/dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sueldo minimo mensual referencial (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dias laborables / mes (para el asesor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comision sugerida por afiliacion al asesor (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bono de equipo en negociacion - minimo (S//dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bono de equipo en negociacion - recomendado (S//dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bono de equipo en negociacion - maximo (S//dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dias de pago considerados por semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dias que trabaja el equipo por mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PISO ECONOMICO (sanity check de la meta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sueldo minimo por dia (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afiliaciones/dia necesarias para igualar el sueldo minimo (a la comision de arriba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equivalente por hora (jornada de 8h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta de 100/dia vs. ese piso (veces)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BONO DE EQUIPO - EQUIVALENTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por dia (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por semana (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por mes (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECOMENDACIONES OPERATIVAS DE LA LLAMADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horario recomendado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casi no hay movimiento en la manana; sube desde el mediodia y el pico mas alto es a las 7:00 p.m., con buen movimiento entre 5 y 9 p.m. Sugerencia: turnos de 12 p.m. a 9 p.m. (o 1 a 9), en vez de horario de oficina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elegibilidad ampliada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El bono ya no aplica solo a afiliaciones GNV: ahora cuenta la afiliacion de cualquier tipo de vehiculo, lo que hace la meta mas facil de alcanzar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quien decide el reparto interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nosotros damos el bono de equipo y los datos de horas pico. Como Marcia reparte ese dinero entre sus 8 fijos y como arma los turnos, es decision de ella.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTA DE RECONCILIACION CON LA HOJA 'RESUMEN'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este bono de equipo (S/120-160/dia, recomendado S/150) es la cifra real que salio de la negociacion con Marcia y con Rodrigo. Reemplaza al S/200 por cada 500 volanteos que se uso como referencia inicial en la hoja 'Resumen'. Antes de tomar una decision final con las hojas 'Escenario Actual' y 'Estrategias por Quincena', actualiza el parametro 'Bono total por hito' de la hoja Resumen con el monto que se termine de negociar aqui, y ajusta 'Numero de personas fijas' a 8 donde aplique.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0&quot; dias&quot;"/>
     <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="170" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
+    <numFmt numFmtId="171" formatCode="&quot;S/ &quot;#,##0.0;&quot;(S/ &quot;#,##0.0\);\-"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0;\(#,##0.0\);\-"/>
+    <numFmt numFmtId="173" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,8 +405,22 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF833C00"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +457,12 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -388,8 +513,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -397,39 +526,39 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,71 +566,143 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -555,7 +756,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -568,7 +769,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF833C00"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF375623"/>
@@ -760,244 +961,244 @@
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="10" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="9" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="9" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="11" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <f aca="false">30/B16</f>
         <v>3.33333333333333</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="15" t="n">
         <f aca="false">B8*(30/B16)</f>
         <v>666.666666666667</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="14" t="n">
         <f aca="false">2</f>
         <v>2</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="15" t="n">
         <f aca="false">(B11+B12)*2</f>
         <v>400</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="14" t="n">
         <f aca="false">2</f>
         <v>2</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="15" t="n">
         <f aca="false">B8*2</f>
         <v>400</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="14" t="n">
         <f aca="false">2</f>
         <v>2</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="15" t="n">
         <f aca="false">(B13+B14)*2</f>
         <v>400</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">B8*2</f>
         <v>400</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="19" t="n">
         <f aca="false">B8*(30/7)</f>
         <v>857.142857142857</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1025,263 +1226,263 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <f aca="false">B7+C7-1</f>
         <v>7</v>
       </c>
-      <c r="E7" s="21" t="str">
+      <c r="E7" s="22" t="str">
         <f aca="false">IF(C7&lt;=Resumen!$B$15,"Si","No")</f>
         <v>Si</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <f aca="false">IF(E7="Si",Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="G7" s="21" t="str">
+      <c r="G7" s="22" t="str">
         <f aca="false">IF(D7&lt;=30,"Si","No")</f>
         <v>Si</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <f aca="false">D7+1</f>
         <v>8</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <f aca="false">B8+C8-1</f>
         <v>16</v>
       </c>
-      <c r="E8" s="21" t="str">
+      <c r="E8" s="22" t="str">
         <f aca="false">IF(C8&lt;=Resumen!$B$15,"Si","No")</f>
         <v>Si</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <f aca="false">IF(E8="Si",Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="G8" s="21" t="str">
+      <c r="G8" s="22" t="str">
         <f aca="false">IF(D8&lt;=30,"Si","No")</f>
         <v>Si</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="n">
         <f aca="false">D8+1</f>
         <v>17</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <f aca="false">B9+C9-1</f>
         <v>24</v>
       </c>
-      <c r="E9" s="21" t="str">
+      <c r="E9" s="22" t="str">
         <f aca="false">IF(C9&lt;=Resumen!$B$15,"Si","No")</f>
         <v>Si</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <f aca="false">IF(E9="Si",Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="G9" s="21" t="str">
+      <c r="G9" s="22" t="str">
         <f aca="false">IF(D9&lt;=30,"Si","No")</f>
         <v>Si</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <f aca="false">D9+1</f>
         <v>25</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <f aca="false">B10+C10-1</f>
         <v>34</v>
       </c>
-      <c r="E10" s="21" t="str">
+      <c r="E10" s="22" t="str">
         <f aca="false">IF(C10&lt;=Resumen!$B$15,"Si","No")</f>
         <v>Si</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">IF(E10="Si",Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="G10" s="21" t="str">
+      <c r="G10" s="22" t="str">
         <f aca="false">IF(D10&lt;=30,"Si","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <f aca="false">D10+1</f>
         <v>35</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <f aca="false">B11+C11-1</f>
         <v>43</v>
       </c>
-      <c r="E11" s="21" t="str">
+      <c r="E11" s="22" t="str">
         <f aca="false">IF(C11&lt;=Resumen!$B$15,"Si","No")</f>
         <v>Si</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <f aca="false">IF(E11="Si",Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="G11" s="21" t="str">
+      <c r="G11" s="22" t="str">
         <f aca="false">IF(D11&lt;=30,"Si","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <f aca="false">D11+1</f>
         <v>44</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <f aca="false">B12+C12-1</f>
         <v>51</v>
       </c>
-      <c r="E12" s="21" t="str">
+      <c r="E12" s="22" t="str">
         <f aca="false">IF(C12&lt;=Resumen!$B$15,"Si","No")</f>
         <v>Si</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <f aca="false">IF(E12="Si",Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="G12" s="21" t="str">
+      <c r="G12" s="22" t="str">
         <f aca="false">IF(D12&lt;=30,"Si","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23" t="n">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24" t="n">
         <f aca="false">COUNTIF(G7:G12,"Si")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="24" t="n">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="25" t="n">
         <f aca="false">SUMPRODUCT((G7:G12="Si")*F7:F12)</f>
         <v>600</v>
       </c>
@@ -1310,199 +1511,199 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B7),B7&lt;=Resumen!$B$17),Resumen!$B$11,0)+IF(AND(ISNUMBER(C7),C7&lt;=Resumen!$B$17),Resumen!$B$12,0)</f>
         <v>200</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(C7),C7&lt;=Resumen!$B$17),Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B7),B7&lt;=Resumen!$B$17),Resumen!$B$13,0)+IF(AND(ISNUMBER(C7),C7&lt;=Resumen!$B$17),Resumen!$B$14,0)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B8),B8&lt;=Resumen!$B$17),Resumen!$B$11,0)+IF(AND(ISNUMBER(C8),C8&lt;=Resumen!$B$17),Resumen!$B$12,0)</f>
         <v>200</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(C8),C8&lt;=Resumen!$B$17),Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B8),B8&lt;=Resumen!$B$17),Resumen!$B$13,0)+IF(AND(ISNUMBER(C8),C8&lt;=Resumen!$B$17),Resumen!$B$14,0)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B9),B9&lt;=Resumen!$B$17),Resumen!$B$11,0)+IF(AND(ISNUMBER(C9),C9&lt;=Resumen!$B$17),Resumen!$B$12,0)</f>
         <v>200</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(C9),C9&lt;=Resumen!$B$17),Resumen!$B$8,0)</f>
         <v>200</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B9),B9&lt;=Resumen!$B$17),Resumen!$B$13,0)+IF(AND(ISNUMBER(C9),C9&lt;=Resumen!$B$17),Resumen!$B$14,0)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="14" t="n">
+      <c r="C10" s="11"/>
+      <c r="D10" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B10),B10&lt;=Resumen!$B$17),Resumen!$B$11,0)+IF(AND(ISNUMBER(C10),C10&lt;=Resumen!$B$17),Resumen!$B$12,0)</f>
         <v>100</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(C10),C10&lt;=Resumen!$B$17),Resumen!$B$8,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(B10),B10&lt;=Resumen!$B$17),Resumen!$B$13,0)+IF(AND(ISNUMBER(C10),C10&lt;=Resumen!$B$17),Resumen!$B$14,0)</f>
         <v>70</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27" t="n">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28" t="n">
         <f aca="false">SUM(D7:D10)</f>
         <v>700</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="28" t="n">
         <f aca="false">SUM(E7:E10)</f>
         <v>600</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="28" t="n">
         <f aca="false">SUM(F7:F10)</f>
         <v>670</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="24" t="n">
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="25" t="n">
         <f aca="false">D11/(4/2)</f>
         <v>350</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">E11/(4/2)</f>
         <v>300</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">F11/(4/2)</f>
         <v>335</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1518,4 +1719,336 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="35" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="36" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="35" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="38" t="n">
+        <f aca="false">B8/B9</f>
+        <v>43.4615384615385</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="39" t="n">
+        <f aca="false">(B8/B9)/B10</f>
+        <v>21.7307692307692</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="39" t="n">
+        <f aca="false">B19/8</f>
+        <v>2.71634615384615</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="40" t="n">
+        <f aca="false">B7/B19</f>
+        <v>4.60176991150443</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="41" t="n">
+        <f aca="false">B11</f>
+        <v>120</v>
+      </c>
+      <c r="C25" s="41" t="n">
+        <f aca="false">B12</f>
+        <v>150</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <f aca="false">B13</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="43" t="n">
+        <f aca="false">B11*$B$14</f>
+        <v>600</v>
+      </c>
+      <c r="C26" s="43" t="n">
+        <f aca="false">B12*$B$14</f>
+        <v>750</v>
+      </c>
+      <c r="D26" s="43" t="n">
+        <f aca="false">B13*$B$14</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="43" t="n">
+        <f aca="false">B11*$B$15</f>
+        <v>3120</v>
+      </c>
+      <c r="C27" s="43" t="n">
+        <f aca="false">B12*$B$15</f>
+        <v>3900</v>
+      </c>
+      <c r="D27" s="43" t="n">
+        <f aca="false">B13*$B$15</f>
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+    </row>
+    <row r="40" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="47"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A40:D40"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/flujo-incentivos-volanteo.xlsx
+++ b/flujo-incentivos-volanteo.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Escenario Actual" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Estrategias por Quincena" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Datos de Campo (Rodrigo)" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Analisis Real y Calculadora" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="125">
   <si>
     <t xml:space="preserve">Incentivos de Volanteo - Escenario Actual y Estrategias de Pago</t>
   </si>
@@ -290,23 +291,132 @@
   </si>
   <si>
     <t xml:space="preserve">Este bono de equipo (S/120-160/dia, recomendado S/150) es la cifra real que salio de la negociacion con Marcia y con Rodrigo. Reemplaza al S/200 por cada 500 volanteos que se uso como referencia inicial en la hoja 'Resumen'. Antes de tomar una decision final con las hojas 'Escenario Actual' y 'Estrategias por Quincena', actualiza el parametro 'Bono total por hito' de la hoja Resumen con el monto que se termine de negociar aqui, y ajusta 'Numero de personas fijas' a 8 donde aplique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisis Real de Afiliaciones y Calculadora de Meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATOS REALES - EQUIPO FIJO DE MARCIA (por semana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rango de fechas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afiliaciones reales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 ago - 6 set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 - 13 set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 - 20 set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 - 27 set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promedio / Minimo / Maximo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimo semanal real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximo semanal real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATOS REALES - RED GENERAL DE SCOUTS (por semana completa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 - 23 ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 - 30 ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUINCENAS REALES (2 semanas seguidas, equipo de Marcia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suma de 2 semanas seguidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1+S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2+S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3+S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimo / Maximo quincenal real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULADORA - ELIGE UNA META</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta de volanteos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodo (escribe: Semana o Quincena)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bono por periodo cumplido (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESULTADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rango real de referencia (minimo - maximo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factibilidad de la meta elegida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veces que se paga al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasto total del mes (si cumplen cada periodo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota: cambiar la META no cambia el gasto mensual (el bono siempre es S/200 por periodo cumplido, para todo el equipo). Lo que cambia con la meta es que tan facil o dificil es ganarselo; lo que cambia el gasto es el PERIODO elegido (semana vs. quincena). Usa la factibilidad de arriba para elegir una meta creible segun lo que el equipo ya demostro.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0&quot; dias&quot;"/>
     <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="170" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
-    <numFmt numFmtId="171" formatCode="&quot;S/ &quot;#,##0.0;&quot;(S/ &quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0;\(#,##0.0\);\-"/>
-    <numFmt numFmtId="173" formatCode="0.0\x"/>
+    <numFmt numFmtId="169" formatCode="&quot;S/ &quot;#,##0.0;&quot;(S/ &quot;#,##0.0\);\-"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0;\(#,##0.0\);\-"/>
+    <numFmt numFmtId="171" formatCode="0.0\x"/>
+    <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -513,7 +623,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -634,6 +744,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -654,19 +788,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -674,31 +808,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1729,8 +1855,8 @@
   <dimension ref="A1:D40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1741,158 +1867,158 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="10" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="10" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="9" t="n">
         <v>1130</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="10" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="9" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="9" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="9" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="9" t="n">
         <v>160</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="10" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="10" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="38" t="n">
+      <c r="B18" s="30" t="n">
         <f aca="false">B8/B9</f>
         <v>43.4615384615385</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="39" t="n">
+      <c r="B19" s="31" t="n">
         <f aca="false">(B8/B9)/B10</f>
         <v>21.7307692307692</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="39" t="n">
+      <c r="B20" s="31" t="n">
         <f aca="false">B19/8</f>
         <v>2.71634615384615</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="40" t="n">
+      <c r="B21" s="32" t="n">
         <f aca="false">B7/B19</f>
         <v>4.60176991150443</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="33" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
       <c r="B24" s="12" t="s">
         <v>74</v>
@@ -1904,128 +2030,128 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="41" t="n">
+      <c r="B25" s="15" t="n">
         <f aca="false">B11</f>
         <v>120</v>
       </c>
-      <c r="C25" s="41" t="n">
+      <c r="C25" s="15" t="n">
         <f aca="false">B12</f>
         <v>150</v>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="15" t="n">
         <f aca="false">B13</f>
         <v>160</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="42" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="43" t="n">
+      <c r="B26" s="25" t="n">
         <f aca="false">B11*$B$14</f>
         <v>600</v>
       </c>
-      <c r="C26" s="43" t="n">
+      <c r="C26" s="25" t="n">
         <f aca="false">B12*$B$14</f>
         <v>750</v>
       </c>
-      <c r="D26" s="43" t="n">
+      <c r="D26" s="25" t="n">
         <f aca="false">B13*$B$14</f>
         <v>800</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="42" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="43" t="n">
+      <c r="B27" s="25" t="n">
         <f aca="false">B11*$B$15</f>
         <v>3120</v>
       </c>
-      <c r="C27" s="43" t="n">
+      <c r="C27" s="25" t="n">
         <f aca="false">B12*$B$15</f>
         <v>3900</v>
       </c>
-      <c r="D27" s="43" t="n">
+      <c r="D27" s="25" t="n">
         <f aca="false">B13*$B$15</f>
         <v>4160</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="33" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="44" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="44" t="s">
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="44" t="s">
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="44"/>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="45" t="s">
+      <c r="A37" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="46" t="s">
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="47" t="s">
+      <c r="A40" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="47"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2051,4 +2177,385 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="41" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="41" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="41" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="41" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="44" t="n">
+        <f aca="false">AVERAGE(C7:C10)</f>
+        <v>53.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="45" t="n">
+        <f aca="false">MIN(C7:C10)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="45" t="n">
+        <f aca="false">MAX(C7:C10)</f>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="41" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="41" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="41" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="41" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="41" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44" t="n">
+        <f aca="false">AVERAGE(C17:C21)</f>
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="41" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="41" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="41" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="45" t="n">
+        <f aca="false">MIN(B26:B28)</f>
+        <v>72</v>
+      </c>
+      <c r="C29" s="45" t="n">
+        <f aca="false">MAX(B26:B28)</f>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="41" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="47" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="48" t="str">
+        <f aca="false">IF(B33="Semana",C12&amp;" - "&amp;C13,B29&amp;" - "&amp;C29)</f>
+        <v>31 - 91</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="49" t="str">
+        <f aca="false">IF(B32&lt;=IF(B33="Semana",C13,C29),"Dentro de lo ya logrado",IF(B32&lt;=IF(B33="Semana",C13,C29)*1.3,"Exigente, cerca de su mejor marca","Muy por encima de lo demostrado"))</f>
+        <v>Dentro de lo ya logrado</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="44" t="n">
+        <f aca="false">IF(B33="Semana",30/7,30/15)</f>
+        <v>4.28571428571429</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="50" t="n">
+        <f aca="false">B34*B39</f>
+        <v>857.142857142857</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A42:E42"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B33" type="list">
+      <formula1>"Semana,Quincena"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/flujo-incentivos-volanteo.xlsx
+++ b/flujo-incentivos-volanteo.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="134">
   <si>
     <t xml:space="preserve">Incentivos de Volanteo - Escenario Actual y Estrategias de Pago</t>
   </si>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">21 - 27 set</t>
   </si>
   <si>
-    <t xml:space="preserve">Promedio / Minimo / Maximo</t>
+    <t xml:space="preserve">Promedio semanal real</t>
   </si>
   <si>
     <t xml:space="preserve">Minimo semanal real</t>
@@ -353,6 +353,9 @@
     <t xml:space="preserve">Semana 5</t>
   </si>
   <si>
+    <t xml:space="preserve">Promedio / referencia (red de scouts)</t>
+  </si>
+  <si>
     <t xml:space="preserve">QUINCENAS REALES (2 semanas seguidas, equipo de Marcia)</t>
   </si>
   <si>
@@ -371,13 +374,34 @@
     <t xml:space="preserve">Minimo / Maximo quincenal real</t>
   </si>
   <si>
-    <t xml:space="preserve">CALCULADORA - ELIGE UNA META</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta de volanteos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Periodo (escribe: Semana o Quincena)</t>
+    <t xml:space="preserve">PROYECCIONES (extrapoladas del ritmo semanal real)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semanas por mes (factor de extrapolacion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimo mensual estimado (= minimo semanal x semanas/mes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximo mensual estimado (= maximo semanal x semanas/mes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimo estimado a 2 meses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximo estimado a 2 meses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULADORA - ELIGE UNA META (minimo 500, por regla del negocio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta de volanteos (minimo 500)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodo (escribe: Semana, Quincena, Mes o Dos meses)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mes</t>
   </si>
   <si>
     <t xml:space="preserve">Bono por periodo cumplido (S/)</t>
@@ -386,7 +410,10 @@
     <t xml:space="preserve">RESULTADOS</t>
   </si>
   <si>
-    <t xml:space="preserve">Rango real de referencia (minimo - maximo)</t>
+    <t xml:space="preserve">Minimo real/estimado de referencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximo real/estimado de referencia</t>
   </si>
   <si>
     <t xml:space="preserve">Factibilidad de la meta elegida</t>
@@ -398,14 +425,14 @@
     <t xml:space="preserve">Gasto total del mes (si cumplen cada periodo)</t>
   </si>
   <si>
-    <t xml:space="preserve">Nota: cambiar la META no cambia el gasto mensual (el bono siempre es S/200 por periodo cumplido, para todo el equipo). Lo que cambia con la meta es que tan facil o dificil es ganarselo; lo que cambia el gasto es el PERIODO elegido (semana vs. quincena). Usa la factibilidad de arriba para elegir una meta creible segun lo que el equipo ya demostro.</t>
+    <t xml:space="preserve">Nota: la meta minima es 500 por regla del negocio. Semana y Quincena usan datos REALES; Mes y Dos meses son ESTIMADOS (se extrapola el rango semanal real x el factor de arriba), porque todavia no hay un mes completo de registros. Cambiar la META no cambia el gasto mensual (el bono siempre es S/200 por periodo cumplido, para todo el equipo); lo que cambia el gasto es el PERIODO elegido.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -416,7 +443,8 @@
     <numFmt numFmtId="171" formatCode="0.0\x"/>
     <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
+    <numFmt numFmtId="174" formatCode="0.00"/>
+    <numFmt numFmtId="175" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -808,15 +836,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="174" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -824,7 +852,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2184,10 +2212,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
@@ -2385,7 +2413,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="42" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B22" s="43"/>
       <c r="C22" s="44" t="n">
@@ -2395,7 +2423,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B24" s="39"/>
       <c r="C24" s="39"/>
@@ -2407,12 +2435,12 @@
         <v>47</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B26" s="41" t="n">
         <v>141</v>
@@ -2420,7 +2448,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="41" t="n">
         <v>122</v>
@@ -2428,7 +2456,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="41" t="n">
         <v>72</v>
@@ -2436,7 +2464,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="45" t="n">
         <f aca="false">MIN(B26:B28)</f>
@@ -2449,7 +2477,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="39" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="39"/>
       <c r="C31" s="39"/>
@@ -2458,95 +2486,158 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" s="41" t="n">
-        <v>70</v>
+        <v>117</v>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>91</v>
+        <v>118</v>
+      </c>
+      <c r="B33" s="45" t="n">
+        <f aca="false">C12*B32</f>
+        <v>134.23</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" s="47" t="n">
-        <v>200</v>
+        <v>119</v>
+      </c>
+      <c r="B34" s="45" t="n">
+        <f aca="false">C13*B32</f>
+        <v>394.03</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="45" t="n">
+        <f aca="false">C12*B32*2</f>
+        <v>268.46</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B37" s="48" t="str">
-        <f aca="false">IF(B33="Semana",C12&amp;" - "&amp;C13,B29&amp;" - "&amp;C29)</f>
-        <v>31 - 91</v>
+      <c r="A36" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="45" t="n">
+        <f aca="false">C13*B32*2</f>
+        <v>788.06</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="B38" s="49" t="str">
-        <f aca="false">IF(B32&lt;=IF(B33="Semana",C13,C29),"Dentro de lo ya logrado",IF(B32&lt;=IF(B33="Semana",C13,C29)*1.3,"Exigente, cerca de su mejor marca","Muy por encima de lo demostrado"))</f>
-        <v>Dentro de lo ya logrado</v>
-      </c>
+      <c r="A38" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="44" t="n">
-        <f aca="false">IF(B33="Semana",30/7,30/15)</f>
-        <v>4.28571428571429</v>
+        <v>123</v>
+      </c>
+      <c r="B39" s="41" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B40" s="50" t="n">
-        <f aca="false">B34*B39</f>
-        <v>857.142857142857</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
+      <c r="B40" s="47" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="48" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="45" t="n">
+        <f aca="false">IF(B40="Semana",C12,IF(B40="Quincena",B29,IF(B40="Mes",B33,B35)))</f>
+        <v>134.23</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="45" t="n">
+        <f aca="false">IF(B40="Semana",C13,IF(B40="Quincena",C29,IF(B40="Mes",B34,B36)))</f>
+        <v>394.03</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" s="49" t="str">
+        <f aca="false">IF(B39&lt;=B45,"Dentro de lo ya logrado",IF(B39&lt;=B45*1.3,"Exigente, cerca de su mejor marca","Muy por encima de lo demostrado"))</f>
+        <v>Exigente, cerca de su mejor marca</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="44" t="n">
+        <f aca="false">IF(B40="Semana",30/7,IF(B40="Quincena",30/15,IF(B40="Mes",1,0.5)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" s="50" t="n">
+        <f aca="false">B41*B47</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="51"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A50:E50"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B33" type="list">
-      <formula1>"Semana,Quincena"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B40" type="list">
+      <formula1>"Semana,Quincena,Mes,Dos meses"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/flujo-incentivos-volanteo.xlsx
+++ b/flujo-incentivos-volanteo.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Estrategias por Quincena" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Datos de Campo (Rodrigo)" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Analisis Real y Calculadora" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Reunion Marcia (28 set)" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="168">
   <si>
     <t xml:space="preserve">Incentivos de Volanteo - Escenario Actual y Estrategias de Pago</t>
   </si>
@@ -426,13 +427,115 @@
   </si>
   <si>
     <t xml:space="preserve">Nota: la meta minima es 500 por regla del negocio. Semana y Quincena usan datos REALES; Mes y Dos meses son ESTIMADOS (se extrapola el rango semanal real x el factor de arriba), porque todavia no hay un mes completo de registros. Cambiar la META no cambia el gasto mensual (el bono siempre es S/200 por periodo cumplido, para todo el equipo); lo que cambia el gasto es el PERIODO elegido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reunion con Marcia (proveedora) - 28 de Setiembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESUMEN EJECUTIVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De los 8 fijos planeados, hoy Marcia tiene realmente activos a unos 4 (Claudia es la mas constante; Hector dejo de responder; Misael y Janet recien estarian por sumarse). El equipo completo esta rindiendo ~15 registros/dia ahora mismo, por debajo de su propio promedio historico de 20-25/dia, por la campana electoral municipal de este domingo: los conductores desconfian de dar su telefono o DNI porque piensan que es propaganda politica. Marcia espera que mejore desde el lunes siguiente a las elecciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATOS CLAVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fijos activos hoy (de 8 planeados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimiento del equipo hoy (bajo por elecciones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~15/dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promedio historico del equipo (fijos, antes de elecciones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-25/dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejor dia registrado, con activacion de Marcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasta 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claudia sola (sin activacion), jornada partida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13-15/dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claudia con activacion de Marcia (megafono, acompanada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/dia (mejor dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo multimarca (10+ personas, aporte secundario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~20/dia combinado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joaquin (multimarca, mejor del grupo) solo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3/dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joaquin en activacion con apoyo de Marcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~13/dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRUCTURA DEL EQUIPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fijos: exclusivos, con polo y merchandise, pagados a diario (Claudia) o semanal (el resto). Multimarca: mas de 10 personas que ya trabajan para InDrive, Cabify, Didi, etc. Nos atienden como algo secundario (priorizan su marca principal), asi que cada uno rinde menos, pero entre todos suman otro ~20/dia al total del equipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL EFECTO "ACTIVACION"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando Marcia sale a acompanar en campo (con megafono, mercadeo visible), el rendimiento individual casi se duplica: Claudia pasa de 13-15 sola a 25 acompanada; Joaquin (multimarca) pasa de 1-3 solo a 13 en activacion. Programar activaciones periodicas es una palanca real para subir el volumen del equipo, no solo depender de que cada quien trabaje solo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEJORAS OPERATIVAS EN CURSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Chatbot: todavia no autocompleta el telefono del conductor, lo que obliga a pedirlo a mano y genera desconfianza; el equipo de Rodrigo lo esta arreglando. 2) Guion mas empatico para pedir datos personales (explicar que es para dar seguimiento y beneficios, no para mal uso). 3) Afiches en postes cerca de grifos (alcance limitado: llega a peatones, no tanto a conductores, pero bajo costo). 4) Mejorar la pagina de puntos/canje: hoy no explica bien el catalogo de premios, los sorteos ni los auspiciadores, lo que reduce el interes del conductor en afiliarse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO REAL DEL BONO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El tramo de 500 registros ya se completo y el bono de S/200 YA FUE PAGADO. Marcia ya acumulo ~200 registros adicionales hacia el siguiente 500, y pidio directamente un ANTICIPO sobre ese avance para no quedar en deuda con su gente. Esto es una validacion real de que un esquema de tramos (Estrategia 1 o 3 de la pestana de estrategias) no es solo teoria: la proveedora ya lo esta pidiendo en la practica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A TENER EN CUENTA PARA LA ESTRATEGIA DE PAGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodrigo cerro la reunion diciendo que el incentivo adicional se esta afinando para evaluarse DE FORMA SEMANAL, no quincenal, porque Marcia paga a su gente a diario o semanal y necesita que el flujo de caja de la empresa calce con ese ritmo (ella misma lo pidio: podemos seguir el ritmo de pago semanal con los avances?). Esto no contradice el analisis de ahorro de la hoja de Estrategias, pero si sugiere que, en el corto plazo, lo mas practico es evaluar la Estrategia 1 o 3 de forma SEMANAL (no quincenal), aceptando algo mas de frecuencia de pago a cambio de no ahogar la caja de la proveedora.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -441,10 +544,8 @@
     <numFmt numFmtId="169" formatCode="&quot;S/ &quot;#,##0.0;&quot;(S/ &quot;#,##0.0\);\-"/>
     <numFmt numFmtId="170" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="171" formatCode="0.0\x"/>
-    <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="0.00"/>
-    <numFmt numFmtId="175" formatCode="&quot;S/ &quot;#,##0;&quot;(S/ &quot;#,##0\);\-"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="173" formatCode="0.00"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -651,7 +752,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -796,68 +897,52 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2215,11 +2300,11 @@
   <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2231,27 +2316,27 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="36" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>91</v>
       </c>
@@ -2262,90 +2347,90 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="10" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="40" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="10" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="40" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="10" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="10" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="44" t="n">
+      <c r="B11" s="23"/>
+      <c r="C11" s="36" t="n">
         <f aca="false">AVERAGE(C7:C10)</f>
         <v>53.25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="45" t="n">
+      <c r="B12" s="23"/>
+      <c r="C12" s="24" t="n">
         <f aca="false">MIN(C7:C10)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="40" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="45" t="n">
+      <c r="B13" s="23"/>
+      <c r="C13" s="24" t="n">
         <f aca="false">MAX(C7:C10)</f>
         <v>91</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
         <v>91</v>
       </c>
@@ -2356,81 +2441,81 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="40" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="41" t="n">
+      <c r="C17" s="10" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="40" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="10" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="40" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="10" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="40" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="10" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="40" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="10" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44" t="n">
+      <c r="B22" s="23"/>
+      <c r="C22" s="36" t="n">
         <f aca="false">AVERAGE(C17:C21)</f>
         <v>73.8</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="39" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-    </row>
-    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
         <v>47</v>
       </c>
@@ -2438,191 +2523,191 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="40" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="41" t="n">
+      <c r="B26" s="10" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="40" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="41" t="n">
+      <c r="B27" s="10" t="n">
         <v>122</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="41" t="n">
+      <c r="B28" s="10" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="42" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="45" t="n">
+      <c r="B29" s="24" t="n">
         <f aca="false">MIN(B26:B28)</f>
         <v>72</v>
       </c>
-      <c r="C29" s="45" t="n">
+      <c r="C29" s="24" t="n">
         <f aca="false">MAX(B26:B28)</f>
         <v>141</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="39" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="43" t="s">
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="46" t="n">
+      <c r="B32" s="37" t="n">
         <v>4.33</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="43" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B33" s="45" t="n">
+      <c r="B33" s="24" t="n">
         <f aca="false">C12*B32</f>
         <v>134.23</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="43" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="B34" s="45" t="n">
+      <c r="B34" s="24" t="n">
         <f aca="false">C13*B32</f>
         <v>394.03</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="43" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="45" t="n">
+      <c r="B35" s="24" t="n">
         <f aca="false">C12*B32*2</f>
         <v>268.46</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="43" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="45" t="n">
+      <c r="B36" s="24" t="n">
         <f aca="false">C13*B32*2</f>
         <v>788.06</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="39" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="43" t="s">
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="41" t="n">
+      <c r="B39" s="10" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="47" t="s">
+      <c r="B40" s="38" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="43" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="48" t="n">
+      <c r="B41" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="39" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="43" t="s">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="45" t="n">
+      <c r="B44" s="24" t="n">
         <f aca="false">IF(B40="Semana",C12,IF(B40="Quincena",B29,IF(B40="Mes",B33,B35)))</f>
         <v>134.23</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="43" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="45" t="n">
+      <c r="B45" s="24" t="n">
         <f aca="false">IF(B40="Semana",C13,IF(B40="Quincena",C29,IF(B40="Mes",B34,B36)))</f>
         <v>394.03</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="43" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="49" t="str">
+      <c r="B46" s="39" t="str">
         <f aca="false">IF(B39&lt;=B45,"Dentro de lo ya logrado",IF(B39&lt;=B45*1.3,"Exigente, cerca de su mejor marca","Muy por encima de lo demostrado"))</f>
         <v>Exigente, cerca de su mejor marca</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="43" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="B47" s="44" t="n">
+      <c r="B47" s="36" t="n">
         <f aca="false">IF(B40="Semana",30/7,IF(B40="Quincena",30/15,IF(B40="Mes",1,0.5)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="43" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B48" s="50" t="n">
+      <c r="B48" s="25" t="n">
         <f aca="false">B41*B47</f>
         <v>200</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="51" t="s">
+      <c r="A50" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2649,4 +2734,237 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+    </row>
+    <row r="4" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+    </row>
+    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+    </row>
+    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+    </row>
+    <row r="25" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+    </row>
+    <row r="28" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+    </row>
+    <row r="31" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>